--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119919535</v>
+        <v>119921974</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>89275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,7 +729,7 @@
         <v>570146</v>
       </c>
       <c r="R2" t="n">
-        <v>6621893</v>
+        <v>6621981</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119921974</v>
+        <v>119919645</v>
       </c>
       <c r="B3" t="n">
-        <v>89275</v>
+        <v>94681</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6286</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570146</v>
+        <v>570145</v>
       </c>
       <c r="R3" t="n">
-        <v>6621981</v>
+        <v>6621874</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,11 +879,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119919645</v>
+        <v>119919535</v>
       </c>
       <c r="B4" t="n">
         <v>94681</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570145</v>
+        <v>570146</v>
       </c>
       <c r="R4" t="n">
-        <v>6621874</v>
+        <v>6621893</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119921974</v>
+        <v>119919535</v>
       </c>
       <c r="B2" t="n">
-        <v>89275</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6286</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -729,7 +722,7 @@
         <v>570146</v>
       </c>
       <c r="R2" t="n">
-        <v>6621981</v>
+        <v>6621893</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,7 +790,7 @@
         <v>119919645</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119919535</v>
+        <v>119921974</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>89292</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,31 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,7 +953,7 @@
         <v>570146</v>
       </c>
       <c r="R4" t="n">
-        <v>6621893</v>
+        <v>6621981</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +986,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119919535</v>
+        <v>119919645</v>
       </c>
       <c r="B2" t="n">
         <v>94704</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570146</v>
+        <v>570145</v>
       </c>
       <c r="R2" t="n">
-        <v>6621893</v>
+        <v>6621874</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119919645</v>
+        <v>119919535</v>
       </c>
       <c r="B3" t="n">
         <v>94704</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570145</v>
+        <v>570146</v>
       </c>
       <c r="R3" t="n">
-        <v>6621874</v>
+        <v>6621893</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119919645</v>
+        <v>119919535</v>
       </c>
       <c r="B2" t="n">
         <v>94704</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570145</v>
+        <v>570146</v>
       </c>
       <c r="R2" t="n">
-        <v>6621874</v>
+        <v>6621893</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119919535</v>
+        <v>119919645</v>
       </c>
       <c r="B3" t="n">
         <v>94704</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570146</v>
+        <v>570145</v>
       </c>
       <c r="R3" t="n">
-        <v>6621893</v>
+        <v>6621874</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119919645</v>
+        <v>119921974</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>89292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>6286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570145</v>
+        <v>570146</v>
       </c>
       <c r="R3" t="n">
-        <v>6621874</v>
+        <v>6621981</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,6 +874,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119921974</v>
+        <v>119919645</v>
       </c>
       <c r="B4" t="n">
-        <v>89292</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +923,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6286</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570146</v>
+        <v>570145</v>
       </c>
       <c r="R4" t="n">
-        <v>6621981</v>
+        <v>6621874</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,11 +991,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129135083</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>129135096</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119919535</v>
+        <v>129134365</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570146</v>
+        <v>570164</v>
       </c>
       <c r="R2" t="n">
-        <v>6621893</v>
+        <v>6622028</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,6 +764,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Tallraka</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119921974</v>
+        <v>112743813</v>
       </c>
       <c r="B3" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6286</v>
+        <v>1593</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570146</v>
+        <v>570090</v>
       </c>
       <c r="R3" t="n">
-        <v>6621981</v>
+        <v>6621843</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +882,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -911,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119919645</v>
+        <v>119919487</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570145</v>
+        <v>570194</v>
       </c>
       <c r="R4" t="n">
-        <v>6621874</v>
+        <v>6622039</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,37 +1007,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129135083</v>
+        <v>119919492</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570134</v>
+        <v>570185</v>
       </c>
       <c r="R5" t="n">
-        <v>6621892</v>
+        <v>6622042</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129134384</v>
+        <v>119919535</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,32 +1125,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570166</v>
+        <v>570146</v>
       </c>
       <c r="R6" t="n">
-        <v>6621988</v>
+        <v>6621893</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,11 +1204,6 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1246,37 +1221,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129135096</v>
+        <v>119919645</v>
       </c>
       <c r="B7" t="n">
-        <v>92901</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570146</v>
+        <v>570145</v>
       </c>
       <c r="R7" t="n">
-        <v>6621877</v>
+        <v>6621874</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,12 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,7 +1310,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1349,6 +1325,677 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129134351</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570200</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6622023</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129135083</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570134</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6621892</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129135096</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570146</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6621877</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119921974</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570146</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6621981</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lukt mjöllik, rodnande i  köttet, sp 5,5-6,5x3,5-4,5. Hyfer med söljor.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129134342</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>570200</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6622023</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129134384</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>570166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6621988</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66343-2021 artfynd.xlsx
+++ b/artfynd/A 66343-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112743813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119919487</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119919492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119919535</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119919645</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134351</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135083</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135096</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119921974</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134342</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,8 +2056,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>